--- a/research/traditional_assets/database/data/chile/chile_recreation.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_recreation.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.191</v>
+        <v>-0.0512</v>
       </c>
       <c r="G2">
-        <v>-0.5851851851851851</v>
+        <v>-0.8938053097345133</v>
       </c>
       <c r="H2">
-        <v>-0.5851851851851851</v>
+        <v>-0.8938053097345133</v>
       </c>
       <c r="I2">
-        <v>-0.7703703703703703</v>
+        <v>-1.070796460176991</v>
       </c>
       <c r="J2">
-        <v>-0.7703703703703703</v>
+        <v>-1.070796460176991</v>
       </c>
       <c r="K2">
-        <v>-0.24</v>
+        <v>-0.337</v>
       </c>
       <c r="L2">
-        <v>-1.777777777777778</v>
+        <v>-2.982300884955752</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -636,10 +636,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.0632005903153379</v>
+        <v>0.1117766234195694</v>
       </c>
       <c r="AB2">
-        <v>0.0632005903153379</v>
+        <v>0.1117766234195694</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,22 +660,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.08</v>
+        <v>0.094</v>
       </c>
       <c r="AM2">
-        <v>0.047</v>
+        <v>0.094</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-1.3</v>
+        <v>-1.287234042553191</v>
       </c>
       <c r="AP2">
         <v>-0</v>
       </c>
       <c r="AQ2">
-        <v>-2.212765957446809</v>
+        <v>-1.287234042553191</v>
       </c>
     </row>
     <row r="3">
@@ -695,25 +695,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.191</v>
+        <v>-0.0512</v>
       </c>
       <c r="G3">
-        <v>-0.5851851851851851</v>
+        <v>-0.8938053097345133</v>
       </c>
       <c r="H3">
-        <v>-0.5851851851851851</v>
+        <v>-0.8938053097345133</v>
       </c>
       <c r="I3">
-        <v>-0.7703703703703703</v>
+        <v>-1.070796460176991</v>
       </c>
       <c r="J3">
-        <v>-0.7703703703703703</v>
+        <v>-1.070796460176991</v>
       </c>
       <c r="K3">
-        <v>-0.24</v>
+        <v>-0.337</v>
       </c>
       <c r="L3">
-        <v>-1.777777777777778</v>
+        <v>-2.982300884955752</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.0632005903153379</v>
+        <v>0.1117766234195694</v>
       </c>
       <c r="AB3">
-        <v>0.0632005903153379</v>
+        <v>0.1117766234195694</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,22 +767,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.08</v>
+        <v>0.094</v>
       </c>
       <c r="AM3">
-        <v>0.047</v>
+        <v>0.094</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-1.3</v>
+        <v>-1.287234042553191</v>
       </c>
       <c r="AP3">
         <v>-0</v>
       </c>
       <c r="AQ3">
-        <v>-2.212765957446809</v>
+        <v>-1.287234042553191</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_recreation.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_recreation.xlsx
@@ -587,26 +587,11 @@
           <t>Recreation</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.0512</v>
-      </c>
-      <c r="G2">
-        <v>-0.8938053097345133</v>
-      </c>
-      <c r="H2">
-        <v>-0.8938053097345133</v>
-      </c>
-      <c r="I2">
-        <v>-1.070796460176991</v>
-      </c>
-      <c r="J2">
-        <v>-1.070796460176991</v>
+      <c r="E2">
+        <v>0.314</v>
       </c>
       <c r="K2">
-        <v>-0.337</v>
-      </c>
-      <c r="L2">
-        <v>-2.982300884955752</v>
+        <v>0.016</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1117766234195694</v>
+        <v>0.09116032217165518</v>
       </c>
       <c r="AB2">
-        <v>0.1117766234195694</v>
+        <v>0.09116032217165518</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,22 +645,16 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
-      </c>
-      <c r="AO2">
-        <v>-1.287234042553191</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0</v>
-      </c>
-      <c r="AQ2">
-        <v>-1.287234042553191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -686,7 +665,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Club de Polo y Equitación San Cristóbal S.A. (SNSE:POLO)</t>
+          <t>Sociedad Anonima de Deportes Club de Golf Santiago (SNSE:GOLF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -694,26 +673,11 @@
           <t>Recreation</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0512</v>
-      </c>
-      <c r="G3">
-        <v>-0.8938053097345133</v>
-      </c>
-      <c r="H3">
-        <v>-0.8938053097345133</v>
-      </c>
-      <c r="I3">
-        <v>-1.070796460176991</v>
-      </c>
-      <c r="J3">
-        <v>-1.070796460176991</v>
+      <c r="E3">
+        <v>0.314</v>
       </c>
       <c r="K3">
-        <v>-0.337</v>
-      </c>
-      <c r="L3">
-        <v>-2.982300884955752</v>
+        <v>0.016</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +686,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,7 +695,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -743,10 +707,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1117766234195694</v>
+        <v>0.09116032217165518</v>
       </c>
       <c r="AB3">
-        <v>0.1117766234195694</v>
+        <v>0.09116032217165518</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,22 +731,16 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AO3">
-        <v>-1.287234042553191</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.287234042553191</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
